--- a/outputs/585-41.xlsx
+++ b/outputs/585-41.xlsx
@@ -17,23 +17,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t xml:space="preserve">11604.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">390.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.19</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -115,12 +98,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -316,39 +303,39 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="n">
+      <c r="A1" s="2" t="n">
         <v>11604.67</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="n">
+      <c r="B1" s="2" t="n">
+        <v>11604.67</v>
+      </c>
+      <c r="C1" s="2" t="n">
         <v>390.68</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="n">
+      <c r="D1" s="2" t="n">
+        <v>390.68</v>
+      </c>
+      <c r="E1" s="2" t="n">
         <v>0.28135</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1" t="n">
+      <c r="F1" s="2" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="G1" s="2" t="n">
         <v>16.1921</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
+      <c r="H1" s="2" t="n">
+        <v>16.19</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/585-41.xlsx
+++ b/outputs/585-41.xlsx
@@ -19,11 +19,27 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t xml:space="preserve">11604.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">390.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.281350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.19</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -57,19 +73,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -98,16 +107,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -134,44 +139,44 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -185,63 +190,54 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -259,34 +255,46 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -301,46 +309,37 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.56"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="n">
         <v>11604.67</v>
       </c>
-      <c r="B1" s="2" t="n">
-        <v>11604.67</v>
-      </c>
-      <c r="C1" s="2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>390.68</v>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>390.68</v>
-      </c>
-      <c r="E1" s="2" t="n">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="n">
         <v>0.28135</v>
       </c>
-      <c r="F1" s="2" t="n">
-        <v>0.28135</v>
-      </c>
-      <c r="G1" s="2" t="n">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="n">
         <v>16.1921</v>
       </c>
-      <c r="H1" s="2" t="n">
-        <v>16.19</v>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
